--- a/CodeSystem-tk-administrator-role.xlsx
+++ b/CodeSystem-tk-administrator-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T11:47:00+00:00</t>
+    <t>2026-09-10T06:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-tk-administrator-role.xlsx
+++ b/CodeSystem-tk-administrator-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T06:56:47+00:00</t>
+    <t>2026-09-10T07:38:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
